--- a/data/xlsx/audit_amessefe_essais_comparatif.xlsx
+++ b/data/xlsx/audit_amessefe_essais_comparatif.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,157 +419,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Localité</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>localite_norm</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>present_in_excel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>present_in_db</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>action_suggeree</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>any_mismatch</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>excel_has_vbs</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>excel_n_vbs</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>db_has_vbs</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>db_n_vbs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>mismatch_vbs</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>excel_has_limites</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>excel_n_limites</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>db_has_limites</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>db_n_limites</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>mismatch_limites</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>excel_has_granulo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>excel_n_granulo</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>db_has_granulo</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>db_n_granulo</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>mismatch_granulo</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>excel_has_classif</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>excel_n_classif</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>db_has_classif</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>db_n_classif</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>mismatch_classif</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>excel_has_gonflement</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>excel_n_gonflement</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>db_has_gonflement</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>db_n_gonflement</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>mismatch_gonflement</t>
         </is>
@@ -606,11 +594,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -619,13 +607,13 @@
         <v>3</v>
       </c>
       <c r="I2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -634,13 +622,13 @@
         <v>3</v>
       </c>
       <c r="N2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -649,13 +637,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -707,11 +695,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -720,13 +708,13 @@
         <v>3</v>
       </c>
       <c r="I3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -735,13 +723,13 @@
         <v>3</v>
       </c>
       <c r="N3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -750,13 +738,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -808,11 +796,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_SURPLUS</t>
         </is>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -866,13 +854,13 @@
         <v>0</v>
       </c>
       <c r="X4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -881,13 +869,13 @@
         <v>0</v>
       </c>
       <c r="AC4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -909,11 +897,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -937,13 +925,13 @@
         <v>3</v>
       </c>
       <c r="N5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="b">
         <v>1</v>
@@ -1010,11 +998,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -1038,13 +1026,13 @@
         <v>3</v>
       </c>
       <c r="N6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
@@ -1071,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -1086,10 +1074,10 @@
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1111,11 +1099,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -1139,13 +1127,13 @@
         <v>3</v>
       </c>
       <c r="N7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1212,11 +1200,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -1225,13 +1213,13 @@
         <v>3</v>
       </c>
       <c r="I8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -1240,13 +1228,13 @@
         <v>3</v>
       </c>
       <c r="N8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1255,13 +1243,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -1309,15 +1297,15 @@
         <v>1</v>
       </c>
       <c r="D9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CREER_SONDAGE</t>
         </is>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -1356,13 +1344,13 @@
         <v>3</v>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="b">
         <v>0</v>
@@ -1414,11 +1402,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -1442,13 +1430,13 @@
         <v>3</v>
       </c>
       <c r="N10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="b">
         <v>1</v>
@@ -1515,11 +1503,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -1543,13 +1531,13 @@
         <v>3</v>
       </c>
       <c r="N11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
@@ -1576,10 +1564,10 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
@@ -1591,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1616,11 +1604,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -1629,13 +1617,13 @@
         <v>3</v>
       </c>
       <c r="I12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1644,13 +1632,13 @@
         <v>3</v>
       </c>
       <c r="N12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1659,13 +1647,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -1717,11 +1705,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -1745,13 +1733,13 @@
         <v>3</v>
       </c>
       <c r="N13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
@@ -1818,11 +1806,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -1846,13 +1834,13 @@
         <v>3</v>
       </c>
       <c r="N14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
@@ -1879,10 +1867,10 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
@@ -1894,10 +1882,10 @@
         <v>1</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1919,11 +1907,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -1932,13 +1920,13 @@
         <v>3</v>
       </c>
       <c r="I15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -1947,13 +1935,13 @@
         <v>3</v>
       </c>
       <c r="N15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -1962,13 +1950,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2020,11 +2008,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -2033,13 +2021,13 @@
         <v>3</v>
       </c>
       <c r="I16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -2048,13 +2036,13 @@
         <v>3</v>
       </c>
       <c r="N16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -2063,13 +2051,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
@@ -2121,11 +2109,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -2149,13 +2137,13 @@
         <v>3</v>
       </c>
       <c r="N17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
@@ -2182,10 +2170,10 @@
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="b">
         <v>1</v>
@@ -2197,10 +2185,10 @@
         <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2222,11 +2210,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -2250,13 +2238,13 @@
         <v>3</v>
       </c>
       <c r="N18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
@@ -2265,13 +2253,13 @@
         <v>3</v>
       </c>
       <c r="S18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
@@ -2323,11 +2311,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -2336,13 +2324,13 @@
         <v>3</v>
       </c>
       <c r="I19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
@@ -2351,13 +2339,13 @@
         <v>3</v>
       </c>
       <c r="N19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -2366,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="b">
         <v>1</v>
@@ -2424,11 +2412,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -2452,13 +2440,13 @@
         <v>3</v>
       </c>
       <c r="N20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
@@ -2467,13 +2455,13 @@
         <v>3</v>
       </c>
       <c r="S20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="b">
         <v>1</v>
@@ -2525,11 +2513,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -2553,13 +2541,13 @@
         <v>3</v>
       </c>
       <c r="N21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
@@ -2626,11 +2614,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -2654,13 +2642,13 @@
         <v>3</v>
       </c>
       <c r="N22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
@@ -2727,11 +2715,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -2740,13 +2728,13 @@
         <v>3</v>
       </c>
       <c r="I23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -2755,13 +2743,13 @@
         <v>3</v>
       </c>
       <c r="N23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -2770,13 +2758,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="b">
         <v>1</v>
@@ -2828,11 +2816,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -2841,13 +2829,13 @@
         <v>3</v>
       </c>
       <c r="I24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -2856,13 +2844,13 @@
         <v>3</v>
       </c>
       <c r="N24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -2871,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" t="b">
         <v>1</v>
@@ -2929,11 +2917,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -2957,13 +2945,13 @@
         <v>3</v>
       </c>
       <c r="N25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
@@ -3030,11 +3018,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -3043,13 +3031,13 @@
         <v>3</v>
       </c>
       <c r="I26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -3058,13 +3046,13 @@
         <v>3</v>
       </c>
       <c r="N26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -3073,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" t="b">
         <v>1</v>
@@ -3131,11 +3119,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -3159,13 +3147,13 @@
         <v>3</v>
       </c>
       <c r="N27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="b">
         <v>1</v>
@@ -3232,11 +3220,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -3260,13 +3248,13 @@
         <v>3</v>
       </c>
       <c r="N28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
@@ -3434,11 +3422,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>0</v>
@@ -3462,13 +3450,13 @@
         <v>3</v>
       </c>
       <c r="N30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
@@ -3477,13 +3465,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" t="b">
         <v>1</v>
@@ -3535,11 +3523,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -3548,13 +3536,13 @@
         <v>3</v>
       </c>
       <c r="I31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
@@ -3563,13 +3551,13 @@
         <v>3</v>
       </c>
       <c r="N31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="b">
         <v>0</v>
@@ -3578,13 +3566,13 @@
         <v>0</v>
       </c>
       <c r="S31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" t="b">
         <v>1</v>
@@ -3636,11 +3624,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -3649,13 +3637,13 @@
         <v>3</v>
       </c>
       <c r="I32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
@@ -3664,13 +3652,13 @@
         <v>3</v>
       </c>
       <c r="N32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="b">
         <v>0</v>
@@ -3679,13 +3667,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" t="b">
         <v>1</v>
@@ -3838,11 +3826,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
@@ -3866,13 +3854,13 @@
         <v>3</v>
       </c>
       <c r="N34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="b">
         <v>1</v>
@@ -3939,11 +3927,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
@@ -3967,13 +3955,13 @@
         <v>3</v>
       </c>
       <c r="N35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="b">
         <v>1</v>
@@ -4000,10 +3988,10 @@
         <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="b">
         <v>1</v>
@@ -4015,10 +4003,10 @@
         <v>1</v>
       </c>
       <c r="AD35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -4040,11 +4028,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
@@ -4068,13 +4056,13 @@
         <v>3</v>
       </c>
       <c r="N36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="b">
         <v>1</v>
@@ -4101,10 +4089,10 @@
         <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="b">
         <v>1</v>
@@ -4116,10 +4104,10 @@
         <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4141,11 +4129,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
@@ -4157,10 +4145,10 @@
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -4169,13 +4157,13 @@
         <v>3</v>
       </c>
       <c r="N37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="b">
         <v>1</v>
@@ -4202,10 +4190,10 @@
         <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="b">
         <v>1</v>
@@ -4217,10 +4205,10 @@
         <v>1</v>
       </c>
       <c r="AD37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4242,11 +4230,11 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
@@ -4270,13 +4258,13 @@
         <v>3</v>
       </c>
       <c r="N38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="b">
         <v>1</v>
@@ -4303,10 +4291,10 @@
         <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
@@ -4318,10 +4306,10 @@
         <v>1</v>
       </c>
       <c r="AD38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -4343,11 +4331,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
@@ -4371,13 +4359,13 @@
         <v>3</v>
       </c>
       <c r="N39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="b">
         <v>1</v>
@@ -4444,11 +4432,11 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
@@ -4457,13 +4445,13 @@
         <v>3</v>
       </c>
       <c r="I40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="b">
         <v>1</v>
@@ -4472,13 +4460,13 @@
         <v>3</v>
       </c>
       <c r="N40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="b">
         <v>0</v>
@@ -4487,13 +4475,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="b">
         <v>1</v>
@@ -4545,11 +4533,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
@@ -4573,13 +4561,13 @@
         <v>3</v>
       </c>
       <c r="N41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="b">
         <v>1</v>
@@ -4646,11 +4634,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
@@ -4674,13 +4662,13 @@
         <v>3</v>
       </c>
       <c r="N42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="b">
         <v>1</v>
@@ -4747,11 +4735,11 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
@@ -4775,13 +4763,13 @@
         <v>3</v>
       </c>
       <c r="N43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
@@ -4848,11 +4836,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
@@ -4891,13 +4879,13 @@
         <v>3</v>
       </c>
       <c r="S44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" t="b">
         <v>0</v>
@@ -4949,11 +4937,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
@@ -4962,13 +4950,13 @@
         <v>3</v>
       </c>
       <c r="I45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -4977,13 +4965,13 @@
         <v>3</v>
       </c>
       <c r="N45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
@@ -4992,13 +4980,13 @@
         <v>0</v>
       </c>
       <c r="S45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" t="b">
         <v>1</v>
@@ -5050,11 +5038,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="b">
         <v>1</v>
@@ -5078,13 +5066,13 @@
         <v>3</v>
       </c>
       <c r="N46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="b">
         <v>1</v>
@@ -5252,11 +5240,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
@@ -5280,13 +5268,13 @@
         <v>3</v>
       </c>
       <c r="N48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="b">
         <v>1</v>
@@ -5656,11 +5644,11 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
@@ -5684,13 +5672,13 @@
         <v>3</v>
       </c>
       <c r="N52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
@@ -5757,11 +5745,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
@@ -5785,13 +5773,13 @@
         <v>3</v>
       </c>
       <c r="N53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="b">
         <v>0</v>
@@ -5858,11 +5846,11 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
@@ -5886,13 +5874,13 @@
         <v>3</v>
       </c>
       <c r="N54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
@@ -5955,15 +5943,15 @@
         <v>1</v>
       </c>
       <c r="D55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CREER_SONDAGE</t>
         </is>
       </c>
       <c r="F55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
@@ -6002,13 +5990,13 @@
         <v>3</v>
       </c>
       <c r="S55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" t="b">
         <v>0</v>
@@ -6060,11 +6048,11 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
@@ -6088,13 +6076,13 @@
         <v>3</v>
       </c>
       <c r="N56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" t="b">
         <v>1</v>
@@ -6161,11 +6149,11 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
@@ -6189,13 +6177,13 @@
         <v>3</v>
       </c>
       <c r="N57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="b">
         <v>1</v>
@@ -6262,11 +6250,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
@@ -6290,13 +6278,13 @@
         <v>3</v>
       </c>
       <c r="N58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" t="b">
         <v>1</v>
@@ -6363,11 +6351,11 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
@@ -6391,13 +6379,13 @@
         <v>3</v>
       </c>
       <c r="N59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="b">
         <v>1</v>
@@ -6464,11 +6452,11 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="b">
         <v>1</v>
@@ -6492,13 +6480,13 @@
         <v>3</v>
       </c>
       <c r="N60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" t="b">
         <v>1</v>
@@ -6565,11 +6553,11 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="b">
         <v>1</v>
@@ -6578,13 +6566,13 @@
         <v>3</v>
       </c>
       <c r="I61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
@@ -6593,13 +6581,13 @@
         <v>3</v>
       </c>
       <c r="N61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -6608,13 +6596,13 @@
         <v>0</v>
       </c>
       <c r="S61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V61" t="b">
         <v>1</v>
@@ -6666,11 +6654,11 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
@@ -6694,13 +6682,13 @@
         <v>3</v>
       </c>
       <c r="N62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" t="b">
         <v>1</v>
@@ -6727,10 +6715,10 @@
         <v>1</v>
       </c>
       <c r="Y62" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA62" t="b">
         <v>1</v>
@@ -6742,10 +6730,10 @@
         <v>1</v>
       </c>
       <c r="AD62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -6767,11 +6755,11 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="b">
         <v>1</v>
@@ -6783,10 +6771,10 @@
         <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -6795,13 +6783,13 @@
         <v>3</v>
       </c>
       <c r="N63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" t="b">
         <v>1</v>
@@ -6828,10 +6816,10 @@
         <v>1</v>
       </c>
       <c r="Y63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA63" t="b">
         <v>1</v>
@@ -6843,10 +6831,10 @@
         <v>1</v>
       </c>
       <c r="AD63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -6864,15 +6852,15 @@
         <v>1</v>
       </c>
       <c r="D64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CREER_SONDAGE</t>
         </is>
       </c>
       <c r="F64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="b">
         <v>0</v>
@@ -6911,13 +6899,13 @@
         <v>3</v>
       </c>
       <c r="S64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V64" t="b">
         <v>0</v>
@@ -6969,11 +6957,11 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="b">
         <v>1</v>
@@ -6997,13 +6985,13 @@
         <v>3</v>
       </c>
       <c r="N65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
@@ -7066,15 +7054,15 @@
         <v>1</v>
       </c>
       <c r="D66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CREER_SONDAGE</t>
         </is>
       </c>
       <c r="F66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
@@ -7113,13 +7101,13 @@
         <v>3</v>
       </c>
       <c r="S66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V66" t="b">
         <v>0</v>
@@ -7171,11 +7159,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
@@ -7199,13 +7187,13 @@
         <v>3</v>
       </c>
       <c r="N67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
@@ -7272,11 +7260,11 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="b">
         <v>0</v>
@@ -7300,13 +7288,13 @@
         <v>3</v>
       </c>
       <c r="N68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
@@ -7315,13 +7303,13 @@
         <v>0</v>
       </c>
       <c r="S68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V68" t="b">
         <v>1</v>
@@ -7474,11 +7462,11 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
@@ -7502,13 +7490,13 @@
         <v>3</v>
       </c>
       <c r="N70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="b">
         <v>1</v>
@@ -7575,11 +7563,11 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
@@ -7603,13 +7591,13 @@
         <v>3</v>
       </c>
       <c r="N71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
@@ -7636,10 +7624,10 @@
         <v>1</v>
       </c>
       <c r="Y71" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA71" t="b">
         <v>1</v>
@@ -7651,10 +7639,10 @@
         <v>1</v>
       </c>
       <c r="AD71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -7672,15 +7660,15 @@
         <v>1</v>
       </c>
       <c r="D72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>CREER_SONDAGE</t>
         </is>
       </c>
       <c r="F72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
@@ -7719,13 +7707,13 @@
         <v>3</v>
       </c>
       <c r="S72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V72" t="b">
         <v>0</v>
@@ -7777,11 +7765,11 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
@@ -7790,13 +7778,13 @@
         <v>3</v>
       </c>
       <c r="I73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
@@ -7805,13 +7793,13 @@
         <v>3</v>
       </c>
       <c r="N73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="b">
         <v>0</v>
@@ -7820,13 +7808,13 @@
         <v>0</v>
       </c>
       <c r="S73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V73" t="b">
         <v>1</v>
@@ -7878,11 +7866,11 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="b">
         <v>1</v>
@@ -7906,13 +7894,13 @@
         <v>3</v>
       </c>
       <c r="N74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="b">
         <v>1</v>
@@ -7979,11 +7967,11 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="b">
         <v>1</v>
@@ -8007,13 +7995,13 @@
         <v>3</v>
       </c>
       <c r="N75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="b">
         <v>1</v>
@@ -8080,11 +8068,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
@@ -8108,13 +8096,13 @@
         <v>3</v>
       </c>
       <c r="N76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="b">
         <v>1</v>
@@ -8181,11 +8169,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
@@ -8209,13 +8197,13 @@
         <v>3</v>
       </c>
       <c r="N77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="b">
         <v>1</v>
@@ -8282,11 +8270,11 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="b">
         <v>1</v>
@@ -8295,13 +8283,13 @@
         <v>3</v>
       </c>
       <c r="I78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
@@ -8310,13 +8298,13 @@
         <v>3</v>
       </c>
       <c r="N78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" t="b">
         <v>0</v>
@@ -8325,13 +8313,13 @@
         <v>0</v>
       </c>
       <c r="S78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V78" t="b">
         <v>1</v>
@@ -8383,11 +8371,11 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="b">
         <v>1</v>
@@ -8396,13 +8384,13 @@
         <v>3</v>
       </c>
       <c r="I79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
@@ -8411,13 +8399,13 @@
         <v>3</v>
       </c>
       <c r="N79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
@@ -8426,13 +8414,13 @@
         <v>0</v>
       </c>
       <c r="S79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V79" t="b">
         <v>1</v>
@@ -8484,11 +8472,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="b">
         <v>1</v>
@@ -8497,13 +8485,13 @@
         <v>3</v>
       </c>
       <c r="I80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
@@ -8512,13 +8500,13 @@
         <v>3</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="b">
         <v>0</v>
@@ -8527,13 +8515,13 @@
         <v>0</v>
       </c>
       <c r="S80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V80" t="b">
         <v>1</v>
@@ -8585,11 +8573,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="b">
         <v>1</v>
@@ -8598,13 +8586,13 @@
         <v>3</v>
       </c>
       <c r="I81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -8613,13 +8601,13 @@
         <v>3</v>
       </c>
       <c r="N81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="b">
         <v>0</v>
@@ -8628,13 +8616,13 @@
         <v>0</v>
       </c>
       <c r="S81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" t="b">
         <v>1</v>
@@ -8686,11 +8674,11 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="b">
         <v>1</v>
@@ -8699,13 +8687,13 @@
         <v>3</v>
       </c>
       <c r="I82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
@@ -8714,13 +8702,13 @@
         <v>3</v>
       </c>
       <c r="N82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="b">
         <v>0</v>
@@ -8729,13 +8717,13 @@
         <v>0</v>
       </c>
       <c r="S82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" t="b">
         <v>1</v>
@@ -8787,11 +8775,11 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="b">
         <v>1</v>
@@ -8800,13 +8788,13 @@
         <v>3</v>
       </c>
       <c r="I83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
@@ -8815,13 +8803,13 @@
         <v>3</v>
       </c>
       <c r="N83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="b">
         <v>0</v>
@@ -8830,13 +8818,13 @@
         <v>0</v>
       </c>
       <c r="S83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" t="b">
         <v>1</v>
@@ -9191,11 +9179,11 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="b">
         <v>0</v>
@@ -9219,13 +9207,13 @@
         <v>3</v>
       </c>
       <c r="N87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="b">
         <v>0</v>
@@ -9292,11 +9280,11 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="b">
         <v>0</v>
@@ -9320,13 +9308,13 @@
         <v>3</v>
       </c>
       <c r="N88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="b">
         <v>0</v>
@@ -9393,11 +9381,11 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="b">
         <v>0</v>
@@ -9421,13 +9409,13 @@
         <v>3</v>
       </c>
       <c r="N89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="b">
         <v>0</v>
@@ -9494,11 +9482,11 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="b">
         <v>1</v>
@@ -9522,13 +9510,13 @@
         <v>3</v>
       </c>
       <c r="N90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="b">
         <v>1</v>
@@ -9595,11 +9583,11 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="b">
         <v>1</v>
@@ -9623,13 +9611,13 @@
         <v>3</v>
       </c>
       <c r="N91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="b">
         <v>1</v>
@@ -9696,11 +9684,11 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="b">
         <v>1</v>
@@ -9709,13 +9697,13 @@
         <v>3</v>
       </c>
       <c r="I92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="b">
         <v>1</v>
@@ -9724,13 +9712,13 @@
         <v>3</v>
       </c>
       <c r="N92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="b">
         <v>0</v>
@@ -9739,13 +9727,13 @@
         <v>0</v>
       </c>
       <c r="S92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V92" t="b">
         <v>1</v>
@@ -9797,11 +9785,11 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>VERIFIER_MIXTE</t>
         </is>
       </c>
       <c r="F93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="b">
         <v>1</v>
@@ -9810,13 +9798,13 @@
         <v>3</v>
       </c>
       <c r="I93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
@@ -9825,13 +9813,13 @@
         <v>3</v>
       </c>
       <c r="N93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="b">
         <v>0</v>
@@ -9840,13 +9828,13 @@
         <v>0</v>
       </c>
       <c r="S93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V93" t="b">
         <v>1</v>
@@ -9894,37 +9882,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>essai</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>excel_localites</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>db_localites</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>excel_total</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>db_total</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>mismatch_count</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>match_pct</t>
         </is>
@@ -9940,19 +9928,19 @@
         <v>75</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
         <v>224</v>
       </c>
       <c r="E2" t="n">
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="3">
@@ -9965,19 +9953,19 @@
         <v>75</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>225</v>
       </c>
       <c r="E3" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="4">
@@ -9990,19 +9978,19 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
         <v>149</v>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -10015,19 +10003,19 @@
         <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" t="n">
         <v>226</v>
       </c>
       <c r="E5" t="n">
-        <v>226</v>
+        <v>298</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -10040,19 +10028,19 @@
         <v>76</v>
       </c>
       <c r="C6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="n">
         <v>228</v>
       </c>
       <c r="E6" t="n">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -10066,84 +10054,4430 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Localité</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>localite_norm</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>action_suggeree</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>present_in_excel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>present_in_db</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>excel_n_vbs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>db_n_vbs</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>excel_n_limites</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>db_n_limites</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>excel_n_granulo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>db_n_granulo</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>excel_n_classif</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>db_n_classif</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>excel_n_gonflement</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>db_n_gonflement</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Akié</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>akie</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CREER_SONDAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kpiné (Woumé)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>kpine (woume)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CREER_SONDAGE</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pitiah</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pitiah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CREER_SONDAGE</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sanfatoule</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sanfatoule</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CREER_SONDAGE</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sotouboua (Soudè)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sotouboua (soude)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CREER_SONDAGE</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Adjengré (Pounpouni)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>adjengre (pounpouni)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Akéi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>akei</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Alibi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>alibi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Apéssito</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>apessito</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bassar ( kpankissi)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>bassar (kpankissi)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bitchabé</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bitchabe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bohou</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bohou</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Campement</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>campement</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dimouri</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dimouri</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Djidjolé</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>djidjole</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Doutikopé</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>doutikope</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kabou (okpandoupo)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>kabou (okpandoupo)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Katore</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>katore</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Komah</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>komah</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Korbongou</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>korbongou</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Koudjoundè</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>koudjounde</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Koudjouwdè</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>koudjouwde</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kpadapé</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>kpadape</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kpawa</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>kpawa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kpimé Séva</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>kpime seva</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kpimé Tomégbé</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>kpime tomegbe</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kpimé Woumé</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>kpime woume</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kpodzi</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>kpodzi</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lama Feing</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>lama feing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Lama Tchamdè</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>lama tchamde</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Lama-tessi</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>lama-tessi</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Lavié Apédomé</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>lavie apedome</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Pittah</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>pittah</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sanfatoute</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sanfatoute</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Solim</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>solim</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tchalo</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>tchalo</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tchamba</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>tchamba</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tchamdè</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>tchamde</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tchitchao</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tchitchao</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Womé Cascade</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wome cascade</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Womé Ville</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wome ville</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Womé Zongo</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wome zongo</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Yade</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>yade</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Zomayi</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>zomayi</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>IMPORTER_ESSAIS</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Abobo</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>abobo</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Adétikopé</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>adetikope</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Agotivé</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>agotive</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" t="n">
+        <v>9</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aképé</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>akepe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>3</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Anié</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>anie</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>9</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3</v>
+      </c>
+      <c r="O50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Apéhéme</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>apeheme</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Apéyéyémé</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>apeyeyeme</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3</v>
+      </c>
+      <c r="L52" t="n">
+        <v>3</v>
+      </c>
+      <c r="M52" t="n">
+        <v>9</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3</v>
+      </c>
+      <c r="O52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Assahoun</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>assahoun</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Badja</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>badja</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3</v>
+      </c>
+      <c r="L54" t="n">
+        <v>3</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Badomé</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>badome</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>9</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Belgique</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>belgique</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Dalavé</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>dalave</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Dikamé</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>dikame</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Djagblé</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>djagble</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3</v>
+      </c>
+      <c r="L59" t="n">
+        <v>3</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3</v>
+      </c>
+      <c r="O59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Dzogbékopé</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>dzogbekope</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" t="n">
+        <v>3</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3</v>
+      </c>
+      <c r="O60" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gbatopé</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>gbatope</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3</v>
+      </c>
+      <c r="L61" t="n">
+        <v>3</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3</v>
+      </c>
+      <c r="O61" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Hahotoé</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>hahotoe</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3</v>
+      </c>
+      <c r="L62" t="n">
+        <v>3</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3</v>
+      </c>
+      <c r="O62" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Kadambara</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>kadambara</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3</v>
+      </c>
+      <c r="M63" t="n">
+        <v>9</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3</v>
+      </c>
+      <c r="O63" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Kamina Barrage</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>kamina barrage</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3</v>
+      </c>
+      <c r="M64" t="n">
+        <v>9</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3</v>
+      </c>
+      <c r="O64" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Kamina Dakré</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>kamina dakre</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" t="n">
+        <v>3</v>
+      </c>
+      <c r="M65" t="n">
+        <v>9</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3</v>
+      </c>
+      <c r="O65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Kaniamboua ( Bago )</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>kaniamboua (bago)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3</v>
+      </c>
+      <c r="M66" t="n">
+        <v>9</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3</v>
+      </c>
+      <c r="O66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Kévé</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>keve</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3</v>
+      </c>
+      <c r="O67" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Kovié</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>kovie</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>3</v>
+      </c>
+      <c r="L68" t="n">
+        <v>3</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Mission tové</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>mission tove</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3</v>
+      </c>
+      <c r="L69" t="n">
+        <v>3</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3</v>
+      </c>
+      <c r="O69" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Nyamassila</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>nyamassila</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3</v>
+      </c>
+      <c r="K70" t="n">
+        <v>3</v>
+      </c>
+      <c r="L70" t="n">
+        <v>3</v>
+      </c>
+      <c r="M70" t="n">
+        <v>9</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ountivou</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ountivou</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>3</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3</v>
+      </c>
+      <c r="M71" t="n">
+        <v>9</v>
+      </c>
+      <c r="N71" t="n">
+        <v>3</v>
+      </c>
+      <c r="O71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Sevagan</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>sevagan</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3</v>
+      </c>
+      <c r="O72" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sotouboua ( Sondè )</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>sotouboua (sonde)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" t="n">
+        <v>9</v>
+      </c>
+      <c r="N73" t="n">
+        <v>3</v>
+      </c>
+      <c r="O73" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Srikpui( Togblecopé)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>srikpui (togblecope)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>3</v>
+      </c>
+      <c r="L74" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3</v>
+      </c>
+      <c r="O74" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tekpo</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>tekpo</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3</v>
+      </c>
+      <c r="O75" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Tovégan</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>tovegan</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O76" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Tsévié blévé</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>tsevie bleve</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" t="n">
+        <v>3</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3</v>
+      </c>
+      <c r="O77" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Tsévié dalavémodji</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>tsevie dalavemodji</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3</v>
+      </c>
+      <c r="L78" t="n">
+        <v>3</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Tsévié dévé</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>tsevie deve</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3</v>
+      </c>
+      <c r="L79" t="n">
+        <v>3</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Wli</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>wli</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Zongo 1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>zongo 1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>3</v>
+      </c>
+      <c r="L81" t="n">
+        <v>3</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3</v>
+      </c>
+      <c r="O81" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Zongo 2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>zongo 2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>VERIFIER_MIXTE</t>
+        </is>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>3</v>
+      </c>
+      <c r="L82" t="n">
+        <v>3</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3</v>
+      </c>
+      <c r="O82" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Adjengré ( Pounpoun)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>adjengre (pounpoun)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VERIFIER_SURPLUS</t>
+        </is>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>6</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
